--- a/artfynd/A 54323-2021 artfynd.xlsx
+++ b/artfynd/A 54323-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54323-2021 artfynd.xlsx
+++ b/artfynd/A 54323-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>102126370</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>367079.3500477665</v>
+        <v>367079</v>
       </c>
       <c r="R2" t="n">
-        <v>6605883.451493553</v>
+        <v>6605884</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>104095708</v>
       </c>
       <c r="B3" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>367489.1268661621</v>
+        <v>367489</v>
       </c>
       <c r="R3" t="n">
-        <v>6605648.869924779</v>
+        <v>6605649</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,12 +872,7 @@
         <v>104095709</v>
       </c>
       <c r="B4" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>367205.7320558337</v>
+        <v>367205</v>
       </c>
       <c r="R4" t="n">
-        <v>6605593.469290658</v>
+        <v>6605593</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104095707</v>
+        <v>104095710</v>
       </c>
       <c r="B5" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>367016.2990206893</v>
+        <v>367417</v>
       </c>
       <c r="R5" t="n">
-        <v>6605709.718469639</v>
+        <v>6605657</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,12 +1066,7 @@
         <v>104095711</v>
       </c>
       <c r="B6" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>367465.8057685515</v>
+        <v>367466</v>
       </c>
       <c r="R6" t="n">
-        <v>6605650.200750993</v>
+        <v>6605650</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104095710</v>
+        <v>104095712</v>
       </c>
       <c r="B7" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>367416.7699381579</v>
+        <v>367385</v>
       </c>
       <c r="R7" t="n">
-        <v>6605657.004423358</v>
+        <v>6605600</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104095712</v>
+        <v>104095713</v>
       </c>
       <c r="B8" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>367384.7586114601</v>
+        <v>367337</v>
       </c>
       <c r="R8" t="n">
-        <v>6605599.308732902</v>
+        <v>6605583</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1325,9 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104095713</v>
+        <v>104095707</v>
       </c>
       <c r="B9" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>367336.9279347552</v>
+        <v>367017</v>
       </c>
       <c r="R9" t="n">
-        <v>6605582.742719405</v>
+        <v>6605710</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1422,9 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
